--- a/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\07.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEEB3A7-E846-48A6-8201-DFA0701BDBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3774F6E-BF3E-475D-ABBE-0C59EA7D066F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18765" yWindow="-7170" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="236">
   <si>
     <t>DATE</t>
   </si>
@@ -721,6 +721,33 @@
   </si>
   <si>
     <t>LANTANGPEO</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
   </si>
 </sst>
 </file>
@@ -1361,14 +1388,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:EA24"/>
+  <dimension ref="A1:EJ24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.453125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="22" width="8.7265625" customWidth="1"/>
-    <col min="23" max="29" width="8.7265625" style="1" customWidth="1"/>
-    <col min="30" max="36" width="8.7265625" customWidth="1"/>
+    <col min="1" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="22" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="23" max="29" width="8.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="30" max="35" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="8.7265625" customWidth="1"/>
     <col min="37" max="37" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="8.7265625" style="91"/>
     <col min="40" max="40" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -1386,10 +1414,13 @@
     <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="127" max="127" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="130" max="130" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:131" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:140" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
@@ -1780,11 +1811,38 @@
       <c r="DZ1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="EA1" s="28" t="s">
+      <c r="EA1" s="81" t="s">
+        <v>227</v>
+      </c>
+      <c r="EB1" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="EC1" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="ED1" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="EE1" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="EF1" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="EG1" s="81" t="s">
+        <v>233</v>
+      </c>
+      <c r="EH1" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="EI1" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="EJ1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>194</v>
       </c>
@@ -2099,12 +2157,34 @@
       <c r="DX2" s="58"/>
       <c r="DY2" s="71"/>
       <c r="DZ2" s="33" t="str">
-        <f t="shared" ref="DZ2:DZ13" si="31">IF(DX2=0,"NA",DY2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="EA2" s="35"/>
+        <f t="shared" ref="DZ2:DZ22" si="31">IF(DX2=0,"NA",DY2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="EA2" s="58"/>
+      <c r="EB2" s="71"/>
+      <c r="EC2" s="33" t="str">
+        <f t="shared" ref="EC2:EC22" si="32">IF(EA2=0,"NA",EB2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="ED2" s="58">
+        <v>2</v>
+      </c>
+      <c r="EE2" s="71">
+        <v>1.2488425925925925E-2</v>
+      </c>
+      <c r="EF2" s="33">
+        <f t="shared" ref="EF2:EF24" si="33">IF(ED2=0,"NA",EE2-$AD2)</f>
+        <v>8.7037037037037031E-3</v>
+      </c>
+      <c r="EG2" s="58"/>
+      <c r="EH2" s="71"/>
+      <c r="EI2" s="33" t="str">
+        <f t="shared" ref="EI2:EI13" si="34">IF(EG2=0,"NA",EH2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="EJ2" s="35"/>
     </row>
-    <row r="3" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>194</v>
       </c>
@@ -2121,7 +2201,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F22" si="32">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="35">D3&amp;""&amp;E3</f>
         <v>D3</v>
       </c>
       <c r="G3" s="5">
@@ -2157,7 +2237,7 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="33">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="36">J3-I3</f>
         <v>0.10694444444444445</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2186,7 +2266,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="34">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="37">SUM(W3:AB3)</f>
         <v>4.583333333333333E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2205,10 +2285,10 @@
       </c>
       <c r="AI3" s="22"/>
       <c r="AJ3" s="29">
+        <v>9</v>
+      </c>
+      <c r="AK3" s="30">
         <v>8</v>
-      </c>
-      <c r="AK3" s="30">
-        <v>7</v>
       </c>
       <c r="AL3" s="31">
         <v>1</v>
@@ -2432,9 +2512,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA3" s="35"/>
+      <c r="EA3" s="31"/>
+      <c r="EB3" s="32"/>
+      <c r="EC3" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED3" s="31"/>
+      <c r="EE3" s="32"/>
+      <c r="EF3" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG3" s="31">
+        <v>1</v>
+      </c>
+      <c r="EH3" s="34">
+        <v>2.5474537037037039E-2</v>
+      </c>
+      <c r="EI3" s="33">
+        <f t="shared" si="34"/>
+        <v>2.1678240740740741E-2</v>
+      </c>
+      <c r="EJ3" s="35"/>
     </row>
-    <row r="4" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>194</v>
       </c>
@@ -2451,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E1</v>
       </c>
       <c r="G4" s="5">
@@ -2487,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.4305555555555569E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2520,7 +2622,7 @@
       </c>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>6.9328703703703698E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2740,9 +2842,27 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA4" s="35"/>
+      <c r="EA4" s="31"/>
+      <c r="EB4" s="34"/>
+      <c r="EC4" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED4" s="31"/>
+      <c r="EE4" s="34"/>
+      <c r="EF4" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG4" s="31"/>
+      <c r="EH4" s="34"/>
+      <c r="EI4" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ4" s="35"/>
     </row>
-    <row r="5" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>194</v>
       </c>
@@ -2759,7 +2879,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E2</v>
       </c>
       <c r="G5" s="5">
@@ -2795,7 +2915,7 @@
         <v>2</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>6.3888888888888884E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2820,7 +2940,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -3020,9 +3140,27 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA5" s="35"/>
+      <c r="EA5" s="31"/>
+      <c r="EB5" s="32"/>
+      <c r="EC5" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED5" s="31"/>
+      <c r="EE5" s="32"/>
+      <c r="EF5" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG5" s="31"/>
+      <c r="EH5" s="32"/>
+      <c r="EI5" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ5" s="35"/>
     </row>
-    <row r="6" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>194</v>
       </c>
@@ -3039,7 +3177,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E3</v>
       </c>
       <c r="G6" s="5">
@@ -3075,7 +3213,7 @@
         <v>3</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>5.4166666666666696E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -3104,7 +3242,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.1469907407407409E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -3214,11 +3352,11 @@
         <v>4</v>
       </c>
       <c r="BW6" s="34">
-        <v>1.1875E-2</v>
+        <v>9.1087962962962971E-3</v>
       </c>
       <c r="BX6" s="33">
         <f t="shared" si="13"/>
-        <v>4.9305555555555561E-3</v>
+        <v>2.1643518518518531E-3</v>
       </c>
       <c r="BY6" s="31"/>
       <c r="BZ6" s="32"/>
@@ -3340,9 +3478,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA6" s="35"/>
+      <c r="EA6" s="31"/>
+      <c r="EB6" s="32"/>
+      <c r="EC6" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED6" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE6" s="34">
+        <v>1.4421296296296297E-2</v>
+      </c>
+      <c r="EF6" s="33">
+        <f t="shared" si="33"/>
+        <v>7.4768518518518526E-3</v>
+      </c>
+      <c r="EG6" s="31"/>
+      <c r="EH6" s="32"/>
+      <c r="EI6" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ6" s="35"/>
     </row>
-    <row r="7" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>194</v>
       </c>
@@ -3359,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>D1</v>
       </c>
       <c r="G7" s="5">
@@ -3395,7 +3555,7 @@
         <v>4</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.11388888888888887</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3426,7 +3586,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.6145833333333332E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3658,9 +3818,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA7" s="35"/>
+      <c r="EA7" s="31">
+        <v>1</v>
+      </c>
+      <c r="EB7" s="34">
+        <v>3.7557870370370373E-2</v>
+      </c>
+      <c r="EC7" s="33">
+        <f t="shared" si="32"/>
+        <v>3.3761574074074076E-2</v>
+      </c>
+      <c r="ED7" s="31"/>
+      <c r="EE7" s="34"/>
+      <c r="EF7" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG7" s="31"/>
+      <c r="EH7" s="32"/>
+      <c r="EI7" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ7" s="35"/>
     </row>
-    <row r="8" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>194</v>
       </c>
@@ -3677,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>L3</v>
       </c>
       <c r="G8" s="5">
@@ -3713,7 +3895,7 @@
         <v>2</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.11249999999999999</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3740,7 +3922,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.2835648148148145E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3962,9 +4144,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA8" s="35"/>
+      <c r="EA8" s="31">
+        <v>1</v>
+      </c>
+      <c r="EB8" s="70">
+        <v>3.4988425925925923E-2</v>
+      </c>
+      <c r="EC8" s="33">
+        <f t="shared" si="32"/>
+        <v>2.4571759259259258E-2</v>
+      </c>
+      <c r="ED8" s="31"/>
+      <c r="EE8" s="70"/>
+      <c r="EF8" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG8" s="31"/>
+      <c r="EH8" s="70"/>
+      <c r="EI8" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ8" s="35"/>
     </row>
-    <row r="9" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>194</v>
       </c>
@@ -3981,7 +4185,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>L2</v>
       </c>
       <c r="G9" s="5">
@@ -4017,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>9.4444444444444442E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -4046,7 +4250,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.9895833333333336E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -4270,9 +4474,35 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA9" s="35"/>
+      <c r="EA9" s="31"/>
+      <c r="EB9" s="56"/>
+      <c r="EC9" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED9" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE9" s="56">
+        <v>2.8958333333333332E-2</v>
+      </c>
+      <c r="EF9" s="33">
+        <f t="shared" si="33"/>
+        <v>2.4444444444444442E-2</v>
+      </c>
+      <c r="EG9" s="31">
+        <v>1</v>
+      </c>
+      <c r="EH9" s="56">
+        <v>9.7222222222222224E-3</v>
+      </c>
+      <c r="EI9" s="33">
+        <f t="shared" si="34"/>
+        <v>5.2083333333333339E-3</v>
+      </c>
+      <c r="EJ9" s="35"/>
     </row>
-    <row r="10" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>194</v>
       </c>
@@ -4289,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>L1</v>
       </c>
       <c r="G10" s="5">
@@ -4325,7 +4555,7 @@
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.7777777777777835E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -4354,7 +4584,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4.3298611111111114E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -4576,9 +4806,27 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA10" s="35"/>
+      <c r="EA10" s="31"/>
+      <c r="EB10" s="34"/>
+      <c r="EC10" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED10" s="31"/>
+      <c r="EE10" s="34"/>
+      <c r="EF10" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG10" s="31"/>
+      <c r="EH10" s="34"/>
+      <c r="EI10" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ10" s="35"/>
     </row>
-    <row r="11" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>194</v>
       </c>
@@ -4595,7 +4843,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E2</v>
       </c>
       <c r="G11" s="5">
@@ -4631,7 +4879,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>5.4861111111111083E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4660,7 +4908,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.7314814814814818E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4904,9 +5152,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA11" s="35"/>
+      <c r="EA11" s="31"/>
+      <c r="EB11" s="34"/>
+      <c r="EC11" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED11" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE11" s="34">
+        <v>1.3657407407407408E-2</v>
+      </c>
+      <c r="EF11" s="33">
+        <f t="shared" si="33"/>
+        <v>4.953703703703705E-3</v>
+      </c>
+      <c r="EG11" s="31"/>
+      <c r="EH11" s="34"/>
+      <c r="EI11" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ11" s="35"/>
     </row>
-    <row r="12" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>194</v>
       </c>
@@ -4923,7 +5193,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E6</v>
       </c>
       <c r="G12" s="5">
@@ -4959,7 +5229,7 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>8.0555555555555602E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4988,7 +5258,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.0486111111111114E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -5097,14 +5367,14 @@
         <v>NA</v>
       </c>
       <c r="BV12" s="31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BW12" s="34">
-        <v>1.5138888888888889E-2</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="BX12" s="33">
         <f t="shared" si="13"/>
-        <v>7.0833333333333338E-3</v>
+        <v>6.0185185185185168E-4</v>
       </c>
       <c r="BY12" s="31"/>
       <c r="BZ12" s="32"/>
@@ -5222,9 +5492,31 @@
         <f t="shared" si="31"/>
         <v>2.8425925925925927E-2</v>
       </c>
-      <c r="EA12" s="35"/>
+      <c r="EA12" s="31"/>
+      <c r="EB12" s="70"/>
+      <c r="EC12" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED12" s="31">
+        <v>2</v>
+      </c>
+      <c r="EE12" s="70">
+        <v>2.0694444444444446E-2</v>
+      </c>
+      <c r="EF12" s="33">
+        <f t="shared" si="33"/>
+        <v>1.263888888888889E-2</v>
+      </c>
+      <c r="EG12" s="31"/>
+      <c r="EH12" s="70"/>
+      <c r="EI12" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ12" s="35"/>
     </row>
-    <row r="13" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>194</v>
       </c>
@@ -5241,7 +5533,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E4</v>
       </c>
       <c r="G13" s="5">
@@ -5277,7 +5569,7 @@
         <v>6</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.4305555555555569E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -5310,7 +5602,7 @@
       </c>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>7.4502314814814813E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -5516,9 +5808,31 @@
         <f t="shared" si="31"/>
         <v>NA</v>
       </c>
-      <c r="EA13" s="35"/>
+      <c r="EA13" s="31">
+        <v>1</v>
+      </c>
+      <c r="EB13" s="34">
+        <v>3.8425925925925926E-2</v>
+      </c>
+      <c r="EC13" s="33">
+        <f t="shared" si="32"/>
+        <v>1.1979166666666666E-2</v>
+      </c>
+      <c r="ED13" s="31"/>
+      <c r="EE13" s="32"/>
+      <c r="EF13" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG13" s="31"/>
+      <c r="EH13" s="32"/>
+      <c r="EI13" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ13" s="35"/>
     </row>
-    <row r="14" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>194</v>
       </c>
@@ -5535,7 +5849,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>E5</v>
       </c>
       <c r="G14" s="5">
@@ -5571,7 +5885,7 @@
         <v>3</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>5.4166666666666641E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -5600,7 +5914,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4.5798611111111109E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5608,7 +5922,7 @@
       </c>
       <c r="AE14" s="20"/>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="35">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="38">AC14-AD14-AE14</f>
         <v>4.0393518518518516E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5627,25 +5941,25 @@
       <c r="AL14" s="31"/>
       <c r="AM14" s="89"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN22" si="36">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="39">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="37">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="40">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="38">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="41">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="39">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="42">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5657,7 +5971,7 @@
       <c r="BA14" s="31"/>
       <c r="BB14" s="34"/>
       <c r="BC14" s="33" t="str">
-        <f t="shared" ref="BC14:BC22" si="40">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC22" si="43">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BD14" s="31"/>
@@ -5669,13 +5983,13 @@
       <c r="BG14" s="31"/>
       <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="41">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="44">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL22" si="42">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="45">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BM14" s="31">
@@ -5685,19 +5999,19 @@
         <v>8.7847222222222215E-3</v>
       </c>
       <c r="BO14" s="33">
-        <f t="shared" ref="BO14:BO22" si="43">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="46">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>3.3796296296296291E-3</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="44">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="47">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="45">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="48">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31">
@@ -5707,7 +6021,7 @@
         <v>7.9166666666666673E-3</v>
       </c>
       <c r="BX14" s="33">
-        <f t="shared" ref="BX14:BX22" si="46">IF(BV14=0,"NA",BW14-$AD14)</f>
+        <f t="shared" ref="BX14:BX22" si="49">IF(BV14=0,"NA",BW14-$AD14)</f>
         <v>2.5115740740740749E-3</v>
       </c>
       <c r="BY14" s="31"/>
@@ -5823,12 +6137,34 @@
       <c r="DX14" s="31"/>
       <c r="DY14" s="32"/>
       <c r="DZ14" s="33" t="str">
-        <f t="shared" ref="DZ14:DZ22" si="47">IF(DX14=0,"NA",DY14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="EA14" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA14" s="31"/>
+      <c r="EB14" s="34"/>
+      <c r="EC14" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED14" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE14" s="34">
+        <v>1.7847222222222223E-2</v>
+      </c>
+      <c r="EF14" s="33">
+        <f t="shared" si="33"/>
+        <v>1.2442129629629629E-2</v>
+      </c>
+      <c r="EG14" s="31"/>
+      <c r="EH14" s="32"/>
+      <c r="EI14" s="33" t="str">
+        <f t="shared" ref="EI14:EI22" si="50">IF(EG14=0,"NA",EH14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="EJ14" s="35"/>
     </row>
-    <row r="15" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>194</v>
       </c>
@@ -5845,7 +6181,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>L6</v>
       </c>
       <c r="G15" s="5">
@@ -5881,7 +6217,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.6388888888888951E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5910,7 +6246,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>6.3287037037037044E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5918,7 +6254,7 @@
       </c>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>4.2905092592592599E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5941,7 +6277,7 @@
         <v>2.6527777777777779E-2</v>
       </c>
       <c r="AN15" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>6.145833333333333E-3</v>
       </c>
       <c r="AO15" s="31">
@@ -5951,19 +6287,19 @@
         <v>5.1620370370370372E-2</v>
       </c>
       <c r="AQ15" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>3.1238425925925926E-2</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5975,7 +6311,7 @@
       <c r="BA15" s="31"/>
       <c r="BB15" s="32"/>
       <c r="BC15" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="31"/>
@@ -5987,13 +6323,13 @@
       <c r="BG15" s="31"/>
       <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
       <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="31">
@@ -6003,25 +6339,25 @@
         <v>2.6886574074074073E-2</v>
       </c>
       <c r="BO15" s="33">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>6.5046296296296276E-3</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31"/>
       <c r="BW15" s="34"/>
       <c r="BX15" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY15" s="31"/>
@@ -6141,12 +6477,34 @@
       <c r="DX15" s="31"/>
       <c r="DY15" s="32"/>
       <c r="DZ15" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA15" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA15" s="31"/>
+      <c r="EB15" s="34"/>
+      <c r="EC15" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED15" s="31"/>
+      <c r="EE15" s="34"/>
+      <c r="EF15" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG15" s="31">
+        <v>1</v>
+      </c>
+      <c r="EH15" s="34">
+        <v>2.6527777777777779E-2</v>
+      </c>
+      <c r="EI15" s="33">
+        <f t="shared" si="50"/>
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="EJ15" s="35"/>
     </row>
-    <row r="16" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>194</v>
       </c>
@@ -6163,7 +6521,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>D5</v>
       </c>
       <c r="G16" s="5">
@@ -6199,7 +6557,7 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.7777777777777724E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -6228,7 +6586,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4.7233796296296295E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -6236,7 +6594,7 @@
       </c>
       <c r="AE16" s="20"/>
       <c r="AF16" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>4.2974537037037033E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -6247,33 +6605,37 @@
       </c>
       <c r="AI16" s="22"/>
       <c r="AJ16" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK16" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL16" s="31"/>
       <c r="AM16" s="89"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="AO16" s="31"/>
-      <c r="AP16" s="34"/>
-      <c r="AQ16" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="AO16" s="31">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="34">
+        <v>1.4467592592592593E-2</v>
+      </c>
+      <c r="AQ16" s="33">
+        <f t="shared" si="40"/>
+        <v>1.0208333333333333E-2</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -6289,7 +6651,7 @@
         <v>3.1770833333333331E-2</v>
       </c>
       <c r="BC16" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2.751157407407407E-2</v>
       </c>
       <c r="BD16" s="31"/>
@@ -6301,31 +6663,31 @@
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
       <c r="BL16" s="56" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM16" s="31"/>
       <c r="BN16" s="34"/>
       <c r="BO16" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
       <c r="BT16" s="32"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV16" s="31">
@@ -6335,7 +6697,7 @@
         <v>3.9884259259259258E-2</v>
       </c>
       <c r="BX16" s="33">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>3.5624999999999997E-2</v>
       </c>
       <c r="BY16" s="31"/>
@@ -6443,12 +6805,42 @@
       <c r="DX16" s="31"/>
       <c r="DY16" s="34"/>
       <c r="DZ16" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA16" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA16" s="31">
+        <v>2</v>
+      </c>
+      <c r="EB16" s="34">
+        <v>7.6851851851851855E-3</v>
+      </c>
+      <c r="EC16" s="33">
+        <f t="shared" si="32"/>
+        <v>3.425925925925926E-3</v>
+      </c>
+      <c r="ED16" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE16" s="34">
+        <v>2.087962962962963E-2</v>
+      </c>
+      <c r="EF16" s="33">
+        <f t="shared" si="33"/>
+        <v>1.6620370370370369E-2</v>
+      </c>
+      <c r="EG16" s="31">
+        <v>1</v>
+      </c>
+      <c r="EH16" s="34">
+        <v>1.9942129629629629E-2</v>
+      </c>
+      <c r="EI16" s="33">
+        <f t="shared" si="50"/>
+        <v>1.5682870370370368E-2</v>
+      </c>
+      <c r="EJ16" s="35"/>
     </row>
-    <row r="17" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>194</v>
       </c>
@@ -6465,7 +6857,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>D4</v>
       </c>
       <c r="G17" s="5">
@@ -6501,7 +6893,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.4305555555555569E-2</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -6530,7 +6922,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.7337962962962966E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -6538,7 +6930,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>4.4143518518518519E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -6549,33 +6941,37 @@
       </c>
       <c r="AI17" s="22"/>
       <c r="AJ17" s="29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK17" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL17" s="31"/>
       <c r="AM17" s="89"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="AO17" s="31"/>
-      <c r="AP17" s="34"/>
-      <c r="AQ17" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="AO17" s="31">
+        <v>2</v>
+      </c>
+      <c r="AP17" s="34">
+        <v>4.6759259259259257E-2</v>
+      </c>
+      <c r="AQ17" s="33">
+        <f t="shared" si="40"/>
+        <v>3.3564814814814811E-2</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -6587,7 +6983,7 @@
       <c r="BA17" s="31"/>
       <c r="BB17" s="34"/>
       <c r="BC17" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BD17" s="31"/>
@@ -6599,13 +6995,13 @@
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="31">
@@ -6615,25 +7011,25 @@
         <v>2.9097222222222222E-2</v>
       </c>
       <c r="BO17" s="33">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>1.590277777777778E-2</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
       <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31"/>
       <c r="BW17" s="32"/>
       <c r="BX17" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY17" s="31"/>
@@ -6741,12 +7137,42 @@
       <c r="DX17" s="31"/>
       <c r="DY17" s="34"/>
       <c r="DZ17" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA17" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA17" s="31">
+        <v>1</v>
+      </c>
+      <c r="EB17" s="34">
+        <v>1.6030092592592592E-2</v>
+      </c>
+      <c r="EC17" s="33">
+        <f t="shared" si="32"/>
+        <v>2.8356481481481479E-3</v>
+      </c>
+      <c r="ED17" s="31">
+        <v>1</v>
+      </c>
+      <c r="EE17" s="34">
+        <v>4.659722222222222E-2</v>
+      </c>
+      <c r="EF17" s="33">
+        <f t="shared" si="33"/>
+        <v>3.3402777777777774E-2</v>
+      </c>
+      <c r="EG17" s="31">
+        <v>2</v>
+      </c>
+      <c r="EH17" s="34">
+        <v>3.0439814814814815E-2</v>
+      </c>
+      <c r="EI17" s="33">
+        <f t="shared" si="50"/>
+        <v>1.7245370370370369E-2</v>
+      </c>
+      <c r="EJ17" s="35"/>
     </row>
-    <row r="18" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>194</v>
       </c>
@@ -6763,7 +7189,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>D6</v>
       </c>
       <c r="G18" s="5">
@@ -6799,7 +7225,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>6.3194444444444386E-2</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -6828,7 +7254,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4.8182870370370369E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6836,7 +7262,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>4.3518518518518519E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6855,7 +7281,7 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="89"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="31">
@@ -6865,19 +7291,19 @@
         <v>8.7615740740740744E-3</v>
       </c>
       <c r="AQ18" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>4.0972222222222226E-3</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6893,7 +7319,7 @@
         <v>2.8356481481481483E-2</v>
       </c>
       <c r="BC18" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2.3692129629629632E-2</v>
       </c>
       <c r="BD18" s="31"/>
@@ -6905,37 +7331,37 @@
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="31"/>
       <c r="BN18" s="34"/>
       <c r="BO18" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
       <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="31"/>
       <c r="BW18" s="32"/>
       <c r="BX18" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY18" s="31"/>
@@ -7051,12 +7477,34 @@
         <v>2.1759259259259259E-2</v>
       </c>
       <c r="DZ18" s="33">
-        <f t="shared" si="47"/>
+        <f t="shared" si="31"/>
         <v>1.7094907407407406E-2</v>
       </c>
-      <c r="EA18" s="35"/>
+      <c r="EA18" s="31">
+        <v>5</v>
+      </c>
+      <c r="EB18" s="34">
+        <v>6.6898148148148151E-3</v>
+      </c>
+      <c r="EC18" s="33">
+        <f t="shared" si="32"/>
+        <v>2.0254629629629633E-3</v>
+      </c>
+      <c r="ED18" s="31"/>
+      <c r="EE18" s="34"/>
+      <c r="EF18" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG18" s="31"/>
+      <c r="EH18" s="34"/>
+      <c r="EI18" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ18" s="35"/>
     </row>
-    <row r="19" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>194</v>
       </c>
@@ -7073,7 +7521,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>L5</v>
       </c>
       <c r="G19" s="5">
@@ -7109,7 +7557,7 @@
         <v>2</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>7.3611111111111127E-2</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -7136,7 +7584,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5.1493055555555556E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -7144,7 +7592,7 @@
       </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>4.3854166666666666E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -7167,7 +7615,7 @@
         <v>2.6840277777777779E-2</v>
       </c>
       <c r="AN19" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>1.9201388888888889E-2</v>
       </c>
       <c r="AO19" s="31">
@@ -7177,13 +7625,13 @@
         <v>8.773148148148148E-3</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.1342592592592593E-3</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31">
@@ -7193,7 +7641,7 @@
         <v>2.6840277777777779E-2</v>
       </c>
       <c r="AW19" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1.9201388888888889E-2</v>
       </c>
       <c r="AX19" s="31"/>
@@ -7209,7 +7657,7 @@
         <v>2.269675925925926E-2</v>
       </c>
       <c r="BC19" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>1.5057870370370371E-2</v>
       </c>
       <c r="BD19" s="31"/>
@@ -7221,37 +7669,37 @@
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="31"/>
       <c r="BN19" s="34"/>
       <c r="BO19" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
       <c r="BW19" s="32"/>
       <c r="BX19" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY19" s="31"/>
@@ -7359,19 +7807,37 @@
       <c r="DX19" s="31"/>
       <c r="DY19" s="34"/>
       <c r="DZ19" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA19" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA19" s="31"/>
+      <c r="EB19" s="34"/>
+      <c r="EC19" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED19" s="31"/>
+      <c r="EE19" s="34"/>
+      <c r="EF19" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG19" s="31"/>
+      <c r="EH19" s="34"/>
+      <c r="EI19" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ19" s="35"/>
     </row>
-    <row r="20" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G20" s="5"/>
@@ -7391,7 +7857,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R20" s="6"/>
@@ -7406,13 +7872,13 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD20" s="20"/>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AG20" s="21"/>
@@ -7423,25 +7889,25 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="89"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31"/>
       <c r="AP20" s="34"/>
       <c r="AQ20" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="31"/>
       <c r="AS20" s="34"/>
       <c r="AT20" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -7453,7 +7919,7 @@
       <c r="BA20" s="31"/>
       <c r="BB20" s="34"/>
       <c r="BC20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BD20" s="31"/>
@@ -7465,37 +7931,37 @@
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31"/>
       <c r="BN20" s="34"/>
       <c r="BO20" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31"/>
       <c r="BW20" s="34"/>
       <c r="BX20" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY20" s="31"/>
@@ -7603,19 +8069,37 @@
       <c r="DX20" s="31"/>
       <c r="DY20" s="34"/>
       <c r="DZ20" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA20" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA20" s="31"/>
+      <c r="EB20" s="34"/>
+      <c r="EC20" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED20" s="31"/>
+      <c r="EE20" s="34"/>
+      <c r="EF20" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG20" s="31"/>
+      <c r="EH20" s="34"/>
+      <c r="EI20" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ20" s="35"/>
     </row>
-    <row r="21" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G21" s="5"/>
@@ -7635,7 +8119,7 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R21" s="5"/>
@@ -7650,13 +8134,13 @@
       <c r="AA21" s="77"/>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD21" s="78"/>
       <c r="AE21" s="78"/>
       <c r="AF21" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AG21" s="21"/>
@@ -7667,25 +8151,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="89"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -7697,7 +8181,7 @@
       <c r="BA21" s="31"/>
       <c r="BB21" s="34"/>
       <c r="BC21" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BD21" s="31"/>
@@ -7709,37 +8193,37 @@
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
       <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31"/>
       <c r="BN21" s="56"/>
       <c r="BO21" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="31"/>
       <c r="BW21" s="32"/>
       <c r="BX21" s="33" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY21" s="31"/>
@@ -7847,19 +8331,37 @@
       <c r="DX21" s="31"/>
       <c r="DY21" s="56"/>
       <c r="DZ21" s="33" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA21" s="35"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA21" s="31"/>
+      <c r="EB21" s="32"/>
+      <c r="EC21" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED21" s="31"/>
+      <c r="EE21" s="32"/>
+      <c r="EF21" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG21" s="31"/>
+      <c r="EH21" s="56"/>
+      <c r="EI21" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ21" s="35"/>
     </row>
-    <row r="22" spans="1:131" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:140" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="75" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G22" s="11"/>
@@ -7879,7 +8381,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R22" s="11"/>
@@ -7894,13 +8396,13 @@
       <c r="AA22" s="69"/>
       <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD22" s="80"/>
       <c r="AE22" s="80"/>
       <c r="AF22" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AG22" s="24"/>
@@ -7911,25 +8413,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="90"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -7941,7 +8443,7 @@
       <c r="BA22" s="38"/>
       <c r="BB22" s="40"/>
       <c r="BC22" s="41" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BD22" s="38"/>
@@ -7953,37 +8455,37 @@
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38"/>
       <c r="BK22" s="82"/>
       <c r="BL22" s="41" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BM22" s="38"/>
       <c r="BN22" s="40"/>
       <c r="BO22" s="41" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
       <c r="BW22" s="82"/>
       <c r="BX22" s="41" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>NA</v>
       </c>
       <c r="BY22" s="38"/>
@@ -8091,24 +8593,54 @@
       <c r="DX22" s="38"/>
       <c r="DY22" s="40"/>
       <c r="DZ22" s="41" t="str">
-        <f t="shared" si="47"/>
-        <v>NA</v>
-      </c>
-      <c r="EA22" s="39"/>
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA22" s="38"/>
+      <c r="EB22" s="40"/>
+      <c r="EC22" s="41" t="str">
+        <f t="shared" si="32"/>
+        <v>NA</v>
+      </c>
+      <c r="ED22" s="38"/>
+      <c r="EE22" s="40"/>
+      <c r="EF22" s="41" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="EG22" s="38"/>
+      <c r="EH22" s="40"/>
+      <c r="EI22" s="41" t="str">
+        <f t="shared" si="50"/>
+        <v>NA</v>
+      </c>
+      <c r="EJ22" s="39"/>
     </row>
-    <row r="23" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:140" x14ac:dyDescent="0.35">
       <c r="DU23" s="32"/>
       <c r="DV23" s="32"/>
       <c r="DW23" s="33" t="str">
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
+      <c r="ED23" s="32"/>
+      <c r="EE23" s="32"/>
+      <c r="EF23" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
     </row>
-    <row r="24" spans="1:131" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:140" x14ac:dyDescent="0.35">
       <c r="DU24" s="32"/>
       <c r="DV24" s="32"/>
       <c r="DW24" s="33" t="str">
         <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="ED24" s="32"/>
+      <c r="EE24" s="32"/>
+      <c r="EF24" s="33" t="str">
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
     </row>

--- a/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\07.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3774F6E-BF3E-475D-ABBE-0C59EA7D066F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9EB4D0-6D7B-44DE-80FC-46BD1A652A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -5277,20 +5277,16 @@
       </c>
       <c r="AI12" s="22"/>
       <c r="AJ12" s="29">
+        <v>7</v>
+      </c>
+      <c r="AK12" s="30">
         <v>6</v>
       </c>
-      <c r="AK12" s="30">
-        <v>5</v>
-      </c>
-      <c r="AL12" s="31">
-        <v>54</v>
-      </c>
-      <c r="AM12" s="89">
-        <v>8.6574074074074071E-3</v>
-      </c>
-      <c r="AN12" s="33">
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="89"/>
+      <c r="AN12" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>6.0185185185185168E-4</v>
+        <v>NA</v>
       </c>
       <c r="AO12" s="31">
         <v>1</v>
@@ -5302,11 +5298,15 @@
         <f t="shared" si="2"/>
         <v>7.9166666666666656E-3</v>
       </c>
-      <c r="AR12" s="31"/>
-      <c r="AS12" s="32"/>
-      <c r="AT12" s="33" t="str">
+      <c r="AR12" s="31">
+        <v>54</v>
+      </c>
+      <c r="AS12" s="34">
+        <v>8.6574074074074071E-3</v>
+      </c>
+      <c r="AT12" s="33">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>6.0185185185185168E-4</v>
       </c>
       <c r="AU12" s="31"/>
       <c r="AV12" s="32"/>

--- a/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/07.2024/July_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\07.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9EB4D0-6D7B-44DE-80FC-46BD1A652A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814ED425-6B56-417C-9430-CC963005796E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -735,9 +735,6 @@
     <t>MAXN_SWIMMERCRAB</t>
   </si>
   <si>
-    <t>TIME_SWIMMERCRAB</t>
-  </si>
-  <si>
     <t>T1_SWIMMERCRAB</t>
   </si>
   <si>
@@ -748,6 +745,9 @@
   </si>
   <si>
     <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
   </si>
 </sst>
 </file>
@@ -1392,11 +1392,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="6" width="8.7265625" customWidth="1"/>
-    <col min="7" max="22" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="23" max="29" width="8.7265625" style="1" hidden="1" customWidth="1"/>
-    <col min="30" max="35" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="8.7265625" customWidth="1"/>
+    <col min="3" max="22" width="8.7265625" customWidth="1"/>
+    <col min="23" max="29" width="8.7265625" style="1" customWidth="1"/>
+    <col min="30" max="36" width="8.7265625" customWidth="1"/>
     <col min="37" max="37" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="8.7265625" style="91"/>
     <col min="40" max="40" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -1824,19 +1822,19 @@
         <v>230</v>
       </c>
       <c r="EE1" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="EF1" s="59" t="s">
         <v>231</v>
       </c>
-      <c r="EF1" s="59" t="s">
+      <c r="EG1" s="81" t="s">
         <v>232</v>
       </c>
-      <c r="EG1" s="81" t="s">
+      <c r="EH1" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="EH1" s="27" t="s">
+      <c r="EI1" s="59" t="s">
         <v>234</v>
-      </c>
-      <c r="EI1" s="59" t="s">
-        <v>235</v>
       </c>
       <c r="EJ1" s="28" t="s">
         <v>31</v>
@@ -5613,8 +5611,12 @@
         <f t="shared" si="0"/>
         <v>4.8055555555555553E-2</v>
       </c>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
+      <c r="AG13" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH13" s="21">
+        <v>90</v>
+      </c>
       <c r="AI13" s="22"/>
       <c r="AJ13" s="29">
         <v>1</v>
